--- a/vip-links.xlsx
+++ b/vip-links.xlsx
@@ -404,7 +404,7 @@
         <ns0:v>פתיחת הקובץ</ns0:v>
       </ns0:c>
       <ns0:c r="D9" s="8" t="str">
-        <ns0:v>טיוטה להשלמה ולבדיקה משפטית</ns0:v>
+        <ns0:v>זמין</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="10">
